--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_FULL_9_full.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_FULL_9_full.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,891 +414,1349 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39400</v>
+        <v>38496</v>
       </c>
       <c r="B2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39583</v>
+        <v>38587</v>
       </c>
       <c r="B3">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D3">
-        <v>2009</v>
-      </c>
-      <c r="E3">
-        <v>0.2331560026455293</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>39765</v>
+        <v>38678</v>
       </c>
       <c r="B4">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D4">
-        <v>2009</v>
-      </c>
-      <c r="E4">
-        <v>-0.1475798440394471</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>39948</v>
+        <v>38770</v>
       </c>
       <c r="B5">
-        <v>2009</v>
-      </c>
-      <c r="C5">
-        <v>0.02099249989730989</v>
+        <v>2006</v>
       </c>
       <c r="D5">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E5">
-        <v>0.2658381086248385</v>
+        <v>1.396128959430776</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>40130</v>
+        <v>38860</v>
       </c>
       <c r="B6">
-        <v>2009</v>
-      </c>
-      <c r="C6">
-        <v>0.348613976222456</v>
+        <v>2006</v>
       </c>
       <c r="D6">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E6">
-        <v>-0.01626791011750672</v>
+        <v>1.478800353636278</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>40310</v>
+        <v>38953</v>
       </c>
       <c r="B7">
-        <v>2010</v>
-      </c>
-      <c r="C7">
-        <v>-1.307603585337391</v>
+        <v>2006</v>
       </c>
       <c r="D7">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E7">
-        <v>-0.3190550775459045</v>
+        <v>1.555380809477191</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>40494</v>
+        <v>39044</v>
       </c>
       <c r="B8">
-        <v>2010</v>
-      </c>
-      <c r="C8">
-        <v>-0.1384957661262676</v>
+        <v>2006</v>
       </c>
       <c r="D8">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E8">
-        <v>0.8386661657977079</v>
+        <v>1.485471308700004</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>40676</v>
+        <v>39135</v>
       </c>
       <c r="B9">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C9">
-        <v>1.669611657667169</v>
+        <v>1.09621357455234</v>
       </c>
       <c r="D9">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E9">
-        <v>0.5111763828599347</v>
+        <v>1.543011589965704</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>40862</v>
+        <v>39226</v>
       </c>
       <c r="B10">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C10">
-        <v>1.566479473280191</v>
+        <v>2.388329787422805</v>
       </c>
       <c r="D10">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E10">
-        <v>0.7522429756626314</v>
+        <v>2.054906384059163</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>41044</v>
+        <v>39317</v>
       </c>
       <c r="B11">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C11">
-        <v>0.911388480980535</v>
+        <v>1.720975008005254</v>
       </c>
       <c r="D11">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="E11">
-        <v>0.6030710844623588</v>
+        <v>1.56772419027984</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>41228</v>
+        <v>39408</v>
       </c>
       <c r="B12">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C12">
-        <v>0.7307568962937161</v>
+        <v>1.754772933362747</v>
       </c>
       <c r="D12">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="E12">
-        <v>0.625650411734191</v>
+        <v>1.319969052049697</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>41409</v>
+        <v>39504</v>
       </c>
       <c r="B13">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C13">
-        <v>0.5781767497138546</v>
+        <v>0.8599253776059079</v>
       </c>
       <c r="D13">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E13">
-        <v>0.7638490973419954</v>
+        <v>1.485010537071529</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>41592</v>
+        <v>39595</v>
       </c>
       <c r="B14">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C14">
-        <v>0.8188188121642126</v>
+        <v>1.400922024469864</v>
       </c>
       <c r="D14">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E14">
-        <v>0.8799027686248406</v>
+        <v>1.752823409606341</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>41774</v>
+        <v>39686</v>
       </c>
       <c r="B15">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C15">
-        <v>0.9983422690224231</v>
+        <v>1.850047994875026</v>
       </c>
       <c r="D15">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E15">
-        <v>0.8472407659630088</v>
+        <v>1.722286399987927</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>41957</v>
+        <v>39777</v>
       </c>
       <c r="B16">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C16">
-        <v>0.9180054319587239</v>
+        <v>2.213924989827909</v>
       </c>
       <c r="D16">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E16">
-        <v>1.191577176688963</v>
+        <v>2.35021944732241</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>42137</v>
+        <v>39869</v>
       </c>
       <c r="B17">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C17">
-        <v>2.043582053676651</v>
+        <v>1.44755274610755</v>
       </c>
       <c r="D17">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="E17">
-        <v>0.922870897584871</v>
+        <v>1.573512316585579</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>42321</v>
+        <v>39959</v>
       </c>
       <c r="B18">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C18">
-        <v>1.9846842782967</v>
+        <v>0.9777593537953155</v>
       </c>
       <c r="D18">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="E18">
-        <v>1.088188976309357</v>
+        <v>1.505996600083859</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>42503</v>
+        <v>40050</v>
       </c>
       <c r="B19">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C19">
-        <v>1.627179431907866</v>
+        <v>2.39107960738012</v>
       </c>
       <c r="D19">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="E19">
-        <v>0.9048417649844875</v>
+        <v>1.803221630902452</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>42689</v>
+        <v>40141</v>
       </c>
       <c r="B20">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C20">
-        <v>1.755995812646982</v>
+        <v>2.534145137403332</v>
       </c>
       <c r="D20">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="E20">
-        <v>1.107792786355444</v>
+        <v>1.707775012144053</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>42867</v>
+        <v>40233</v>
       </c>
       <c r="B21">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C21">
-        <v>1.275170630186784</v>
+        <v>1.553019351655505</v>
       </c>
       <c r="D21">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="E21">
-        <v>0.9367370402057817</v>
+        <v>1.64082807782806</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>43053</v>
+        <v>40319</v>
       </c>
       <c r="B22">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C22">
-        <v>1.946965557828384</v>
+        <v>2.222831442988071</v>
       </c>
       <c r="D22">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="E22">
-        <v>1.192420150523787</v>
+        <v>1.864287960344368</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>43145</v>
+        <v>40414</v>
       </c>
       <c r="B23">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C23">
-        <v>0.8693402859465182</v>
+        <v>2.768032688479738</v>
       </c>
       <c r="D23">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E23">
-        <v>0.9591991268112832</v>
+        <v>2.121527899809128</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>43235</v>
+        <v>40505</v>
       </c>
       <c r="B24">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C24">
-        <v>1.12840110321426</v>
+        <v>2.088987206093629</v>
       </c>
       <c r="D24">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E24">
-        <v>1.016857026310336</v>
+        <v>1.815484941493861</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>43326</v>
+        <v>40598</v>
       </c>
       <c r="B25">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C25">
-        <v>1.222606696343509</v>
+        <v>2.258680785613976</v>
       </c>
       <c r="D25">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E25">
-        <v>1.078228760229383</v>
+        <v>1.711149295797298</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>43418</v>
+        <v>40687</v>
       </c>
       <c r="B26">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C26">
-        <v>1.064321453542272</v>
+        <v>1.764446094428029</v>
       </c>
       <c r="D26">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E26">
-        <v>0.6327208244686799</v>
+        <v>1.90841960758521</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>43510</v>
+        <v>40871</v>
       </c>
       <c r="B27">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C27">
-        <v>0.5341325240855177</v>
+        <v>1.212532518945841</v>
       </c>
       <c r="D27">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="E27">
-        <v>0.9194690209501699</v>
+        <v>1.823050067264487</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>43600</v>
+        <v>40963</v>
       </c>
       <c r="B28">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C28">
-        <v>1.51898250939253</v>
+        <v>1.565327044852216</v>
       </c>
       <c r="D28">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E28">
-        <v>1.237919511659746</v>
+        <v>1.686948697984181</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>43691</v>
+        <v>41053</v>
       </c>
       <c r="B29">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C29">
-        <v>1.291730672867031</v>
+        <v>1.615295332434563</v>
       </c>
       <c r="D29">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E29">
-        <v>1.029398039926521</v>
+        <v>1.618714658368936</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>43783</v>
+        <v>41144</v>
       </c>
       <c r="B30">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C30">
-        <v>1.361817904277718</v>
+        <v>1.295721896622593</v>
       </c>
       <c r="D30">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E30">
-        <v>1.18054321292711</v>
+        <v>1.506407781687802</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>43875</v>
+        <v>41236</v>
       </c>
       <c r="B31">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C31">
-        <v>0.9671835764273329</v>
+        <v>1.196784623675229</v>
       </c>
       <c r="D31">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="E31">
-        <v>0.9673464562738765</v>
+        <v>1.272951221568497</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>43966</v>
+        <v>41327</v>
       </c>
       <c r="B32">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C32">
-        <v>-1.803908062678516</v>
+        <v>1.533891109777441</v>
       </c>
       <c r="D32">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E32">
-        <v>-0.1348226305034728</v>
+        <v>1.647523644931348</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>44068</v>
+        <v>41418</v>
       </c>
       <c r="B33">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C33">
-        <v>-6.787916126045889</v>
+        <v>0.7568928795189001</v>
       </c>
       <c r="D33">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E33">
-        <v>-6.375423038067662</v>
+        <v>1.465375618478459</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>44159</v>
+        <v>41509</v>
       </c>
       <c r="B34">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C34">
-        <v>-4.352425014431327</v>
+        <v>0.7995164891223316</v>
       </c>
       <c r="D34">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E34">
-        <v>1.562935589653547</v>
+        <v>1.594131419401701</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>44251</v>
+        <v>41600</v>
       </c>
       <c r="B35">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C35">
-        <v>-2.034193111579286</v>
+        <v>0.4723812919182446</v>
       </c>
       <c r="D35">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="E35">
-        <v>0.5359289187882199</v>
+        <v>1.245309094294522</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>44341</v>
+        <v>41695</v>
       </c>
       <c r="B36">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C36">
-        <v>-5.03363841893295</v>
+        <v>1.304395797466706</v>
       </c>
       <c r="D36">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E36">
-        <v>-1.150039807777148</v>
+        <v>1.570514420664715</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>44432</v>
+        <v>41782</v>
       </c>
       <c r="B37">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C37">
-        <v>-3.418142241023947</v>
+        <v>0.6410555646616967</v>
       </c>
       <c r="D37">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E37">
-        <v>0.6186495024194771</v>
+        <v>1.549249030274691</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>44525</v>
+        <v>41968</v>
       </c>
       <c r="B38">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C38">
-        <v>-1.761645650979182</v>
+        <v>0.8777276606119377</v>
       </c>
       <c r="D38">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E38">
-        <v>5.632867463658853</v>
+        <v>1.781555391251755</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>44617</v>
+        <v>42059</v>
       </c>
       <c r="B39">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C39">
-        <v>3.380881785255863</v>
+        <v>1.603794004349579</v>
       </c>
       <c r="D39">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E39">
-        <v>0.7337967053832717</v>
+        <v>1.62363499591649</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>44706</v>
+        <v>42146</v>
       </c>
       <c r="B40">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C40">
-        <v>3.806533520739741</v>
+        <v>1.970233107138508</v>
       </c>
       <c r="D40">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E40">
-        <v>0.6742812297244161</v>
+        <v>1.708622549409577</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>44798</v>
+        <v>42241</v>
       </c>
       <c r="B41">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C41">
-        <v>4.882729126066088</v>
+        <v>2.026504830338349</v>
       </c>
       <c r="D41">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E41">
-        <v>1.301033224791381</v>
+        <v>1.631413870179177</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>44890</v>
+        <v>42332</v>
       </c>
       <c r="B42">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C42">
-        <v>5.20787683103745</v>
+        <v>2.290662253244125</v>
       </c>
       <c r="D42">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E42">
-        <v>2.033577491950478</v>
+        <v>2.449235417553597</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>44981</v>
+        <v>42423</v>
       </c>
       <c r="B43">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C43">
-        <v>0.2392096079561368</v>
+        <v>2.519909491543859</v>
       </c>
       <c r="D43">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E43">
-        <v>0.7832554800447422</v>
+        <v>1.699405280414967</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>45071</v>
+        <v>42514</v>
       </c>
       <c r="B44">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C44">
-        <v>-1.12666423816119</v>
+        <v>2.589364232032954</v>
       </c>
       <c r="D44">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E44">
-        <v>0.3593347800071145</v>
+        <v>1.719212499841682</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>45163</v>
+        <v>42606</v>
       </c>
       <c r="B45">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C45">
-        <v>-0.5016770948104488</v>
+        <v>3.810713811257016</v>
       </c>
       <c r="D45">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E45">
-        <v>0.5616583492845884</v>
+        <v>2.058911954970255</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>45254</v>
+        <v>42698</v>
       </c>
       <c r="B46">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C46">
-        <v>-0.9008525709169657</v>
+        <v>4.109910756223556</v>
       </c>
       <c r="D46">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E46">
-        <v>0.1302881545538925</v>
+        <v>2.713490631531856</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>45345</v>
+        <v>42789</v>
       </c>
       <c r="B47">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C47">
-        <v>0.4485618724060059</v>
+        <v>2.409362954268568</v>
       </c>
       <c r="D47">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E47">
-        <v>0.7433901229060957</v>
+        <v>1.785943746570573</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>45436</v>
+        <v>42878</v>
       </c>
       <c r="B48">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C48">
-        <v>0.2013114615211142</v>
+        <v>1.729122882326695</v>
       </c>
       <c r="D48">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E48">
-        <v>0.5722808921970746</v>
+        <v>1.759400999078675</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>45534</v>
+        <v>42972</v>
       </c>
       <c r="B49">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C49">
-        <v>0.5295399018736102</v>
+        <v>1.971199037447136</v>
       </c>
       <c r="D49">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E49">
-        <v>0.559446195329194</v>
+        <v>1.806347663325902</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>45618</v>
+        <v>43062</v>
       </c>
       <c r="B50">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C50">
-        <v>0.2738544794132602</v>
+        <v>1.660180415270074</v>
       </c>
       <c r="D50">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E50">
-        <v>0.4325397337088255</v>
+        <v>1.208622698681161</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>45713</v>
+        <v>43154</v>
       </c>
       <c r="B51">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C51">
-        <v>0.5192393694020359</v>
+        <v>1.773098682196106</v>
       </c>
       <c r="D51">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E51">
-        <v>0.7362167406303355</v>
+        <v>1.778149483965286</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>45800</v>
+        <v>43244</v>
       </c>
       <c r="B52">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C52">
-        <v>0.9834415437034227</v>
+        <v>1.053253701890378</v>
       </c>
       <c r="D52">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E52">
-        <v>0.8328031391292345</v>
+        <v>1.498847912172341</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>45891</v>
+        <v>43336</v>
       </c>
       <c r="B53">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C53">
-        <v>0.99600290442865</v>
+        <v>1.157904373322105</v>
       </c>
       <c r="D53">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E53">
-        <v>0.7909365692049253</v>
+        <v>1.662435387308858</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
+        <v>43427</v>
+      </c>
+      <c r="B54">
+        <v>2018</v>
+      </c>
+      <c r="C54">
+        <v>1.0578868654878</v>
+      </c>
+      <c r="D54">
+        <v>2019</v>
+      </c>
+      <c r="E54">
+        <v>1.533790036386806</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>43518</v>
+      </c>
+      <c r="B55">
+        <v>2019</v>
+      </c>
+      <c r="C55">
+        <v>2.372554347036382</v>
+      </c>
+      <c r="D55">
+        <v>2020</v>
+      </c>
+      <c r="E55">
+        <v>1.784666562146509</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>43608</v>
+      </c>
+      <c r="B56">
+        <v>2019</v>
+      </c>
+      <c r="C56">
+        <v>1.512087606596935</v>
+      </c>
+      <c r="D56">
+        <v>2020</v>
+      </c>
+      <c r="E56">
+        <v>1.572219740256986</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>43704</v>
+      </c>
+      <c r="B57">
+        <v>2019</v>
+      </c>
+      <c r="C57">
+        <v>1.744120691248807</v>
+      </c>
+      <c r="D57">
+        <v>2020</v>
+      </c>
+      <c r="E57">
+        <v>2.033243961042097</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>43791</v>
+      </c>
+      <c r="B58">
+        <v>2019</v>
+      </c>
+      <c r="C58">
+        <v>1.727536231884064</v>
+      </c>
+      <c r="D58">
+        <v>2020</v>
+      </c>
+      <c r="E58">
+        <v>2.237075695376634</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>43886</v>
+      </c>
+      <c r="B59">
+        <v>2020</v>
+      </c>
+      <c r="C59">
+        <v>2.522355167740797</v>
+      </c>
+      <c r="D59">
+        <v>2021</v>
+      </c>
+      <c r="E59">
+        <v>1.973927267201536</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>43976</v>
+      </c>
+      <c r="B60">
+        <v>2020</v>
+      </c>
+      <c r="C60">
+        <v>2.177023921605392</v>
+      </c>
+      <c r="D60">
+        <v>2021</v>
+      </c>
+      <c r="E60">
+        <v>1.892590492895452</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2">
+        <v>44068</v>
+      </c>
+      <c r="B61">
+        <v>2020</v>
+      </c>
+      <c r="C61">
+        <v>3.175507324846261</v>
+      </c>
+      <c r="D61">
+        <v>2021</v>
+      </c>
+      <c r="E61">
+        <v>2.499012187245953</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>44159</v>
+      </c>
+      <c r="B62">
+        <v>2020</v>
+      </c>
+      <c r="C62">
+        <v>3.806466406787412</v>
+      </c>
+      <c r="D62">
+        <v>2021</v>
+      </c>
+      <c r="E62">
+        <v>3.165947654822987</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>44251</v>
+      </c>
+      <c r="B63">
+        <v>2021</v>
+      </c>
+      <c r="C63">
+        <v>1.806007470948301</v>
+      </c>
+      <c r="D63">
+        <v>2022</v>
+      </c>
+      <c r="E63">
+        <v>1.971781566791986</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2">
+        <v>44341</v>
+      </c>
+      <c r="B64">
+        <v>2021</v>
+      </c>
+      <c r="C64">
+        <v>2.317224818653352</v>
+      </c>
+      <c r="D64">
+        <v>2022</v>
+      </c>
+      <c r="E64">
+        <v>1.918363145155833</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>44432</v>
+      </c>
+      <c r="B65">
+        <v>2021</v>
+      </c>
+      <c r="C65">
+        <v>3.234387268130368</v>
+      </c>
+      <c r="D65">
+        <v>2022</v>
+      </c>
+      <c r="E65">
+        <v>2.376066166812385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
+        <v>44525</v>
+      </c>
+      <c r="B66">
+        <v>2021</v>
+      </c>
+      <c r="C66">
+        <v>3.70707249977813</v>
+      </c>
+      <c r="D66">
+        <v>2022</v>
+      </c>
+      <c r="E66">
+        <v>1.583310261728132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="2">
+        <v>44617</v>
+      </c>
+      <c r="B67">
+        <v>2022</v>
+      </c>
+      <c r="C67">
+        <v>1.779510868863454</v>
+      </c>
+      <c r="D67">
+        <v>2023</v>
+      </c>
+      <c r="E67">
+        <v>2.028691680995243</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="2">
+        <v>44706</v>
+      </c>
+      <c r="B68">
+        <v>2022</v>
+      </c>
+      <c r="C68">
+        <v>0.3845663659276299</v>
+      </c>
+      <c r="D68">
+        <v>2023</v>
+      </c>
+      <c r="E68">
+        <v>1.874923804206174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="2">
+        <v>44798</v>
+      </c>
+      <c r="B69">
+        <v>2022</v>
+      </c>
+      <c r="C69">
+        <v>3.516795174150089</v>
+      </c>
+      <c r="D69">
+        <v>2023</v>
+      </c>
+      <c r="E69">
+        <v>3.372637250562116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="2">
+        <v>44890</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70">
+        <v>1.717176010541088</v>
+      </c>
+      <c r="D70">
+        <v>2023</v>
+      </c>
+      <c r="E70">
+        <v>1.672885884596687</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="2">
+        <v>44981</v>
+      </c>
+      <c r="B71">
+        <v>2023</v>
+      </c>
+      <c r="C71">
+        <v>0.8858219057263916</v>
+      </c>
+      <c r="D71">
+        <v>2024</v>
+      </c>
+      <c r="E71">
+        <v>2.004492356395171</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2">
+        <v>45071</v>
+      </c>
+      <c r="B72">
+        <v>2023</v>
+      </c>
+      <c r="C72">
+        <v>-3.594661838437851</v>
+      </c>
+      <c r="D72">
+        <v>2024</v>
+      </c>
+      <c r="E72">
+        <v>0.4241841204802643</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2">
+        <v>45163</v>
+      </c>
+      <c r="B73">
+        <v>2023</v>
+      </c>
+      <c r="C73">
+        <v>-2.01844567109869</v>
+      </c>
+      <c r="D73">
+        <v>2024</v>
+      </c>
+      <c r="E73">
+        <v>1.07331892100142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2">
+        <v>45254</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="C74">
+        <v>-1.789118639096632</v>
+      </c>
+      <c r="D74">
+        <v>2024</v>
+      </c>
+      <c r="E74">
+        <v>0.7888472770010146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2">
+        <v>45345</v>
+      </c>
+      <c r="B75">
+        <v>2024</v>
+      </c>
+      <c r="C75">
+        <v>1.460582911801533</v>
+      </c>
+      <c r="D75">
+        <v>2025</v>
+      </c>
+      <c r="E75">
+        <v>1.915386549621045</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2">
+        <v>45436</v>
+      </c>
+      <c r="B76">
+        <v>2024</v>
+      </c>
+      <c r="C76">
+        <v>1.360829857501122</v>
+      </c>
+      <c r="D76">
+        <v>2025</v>
+      </c>
+      <c r="E76">
+        <v>1.685192241308342</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2">
+        <v>45534</v>
+      </c>
+      <c r="B77">
+        <v>2024</v>
+      </c>
+      <c r="C77">
+        <v>2.106793980278443</v>
+      </c>
+      <c r="D77">
+        <v>2025</v>
+      </c>
+      <c r="E77">
+        <v>2.208399066696742</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2">
+        <v>45618</v>
+      </c>
+      <c r="B78">
+        <v>2024</v>
+      </c>
+      <c r="C78">
+        <v>2.251694235954238</v>
+      </c>
+      <c r="D78">
+        <v>2025</v>
+      </c>
+      <c r="E78">
+        <v>2.403558697526265</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>45713</v>
+      </c>
+      <c r="B79">
+        <v>2025</v>
+      </c>
+      <c r="C79">
+        <v>3.337407097054701</v>
+      </c>
+      <c r="D79">
+        <v>2026</v>
+      </c>
+      <c r="E79">
+        <v>2.173818084524481</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2">
+        <v>45800</v>
+      </c>
+      <c r="B80">
+        <v>2025</v>
+      </c>
+      <c r="C80">
+        <v>2.309321499638206</v>
+      </c>
+      <c r="D80">
+        <v>2026</v>
+      </c>
+      <c r="E80">
+        <v>1.911286721384009</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2">
+        <v>45891</v>
+      </c>
+      <c r="B81">
+        <v>2025</v>
+      </c>
+      <c r="C81">
+        <v>2.484983295864129</v>
+      </c>
+      <c r="D81">
+        <v>2026</v>
+      </c>
+      <c r="E81">
+        <v>2.065417212611709</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
         <v>45986</v>
       </c>
-      <c r="B54">
+      <c r="B82">
         <v>2025</v>
       </c>
-      <c r="C54">
-        <v>0.8976398032236155</v>
-      </c>
-      <c r="D54">
+      <c r="C82">
+        <v>2.593796720377783</v>
+      </c>
+      <c r="D82">
         <v>2026</v>
       </c>
-      <c r="E54">
-        <v>0.4761827721654566</v>
+      <c r="E82">
+        <v>2.079815056622447</v>
       </c>
     </row>
   </sheetData>
